--- a/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
+++ b/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Taxonomy'!$A$4:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Category Details'!$A$4:$D$19</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,42 @@
     <font>
       <color rgb="001F2933"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F2933"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="FF5B6573"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1E6B52"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F2933"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F2933"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F2933"/>
+    </font>
+    <font>
+      <color rgb="FF1F2933"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +115,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F7F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF172033"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,45 +577,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Open Small Business Records Taxonomy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Start here. The taxonomy describes business responsibilities, not departments or headcount.</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Small Business Records Filing Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Choose where a record belongs by the work it supports. One person may handle several kinds of work. Guide version 0.1.1, 17 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Primary question</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>If this record became wrong or disappeared tomorrow, which business responsibility would have to fix the problem?</t>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Start with the purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>What do you need this record for, and where would you look for it?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Small-business rule</t>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>For a small business</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Categories describe responsibilities, not departments. One person can own several responsibilities.</t>
+          <t>You do not need a department for each category. Use only the categories that help you find and maintain records.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>When two categories both seem right</t>
         </is>
@@ -556,7 +627,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Responsibility beats file format, document type, and department name.</t>
+          <t>Choose by purpose, not whether the record is an email, PDF or spreadsheet.</t>
         </is>
       </c>
     </row>
@@ -566,7 +637,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Financial transaction evidence stays in Finance when finance is its primary purpose.</t>
+          <t>Keep invoices, payments and accounting records in Finance.</t>
         </is>
       </c>
     </row>
@@ -576,7 +647,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Customer relationships stay with Customers; specific execution stays with Projects.</t>
+          <t>Keep customer details in Customers. Keep the work on a particular job in Projects.</t>
         </is>
       </c>
     </row>
@@ -586,7 +657,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Procurement stays with Vendors; resulting purchase invoices normally stay with Finance.</t>
+          <t>Keep supplier selection and ordering in Vendors. Keep purchase invoices in Finance.</t>
         </is>
       </c>
     </row>
@@ -596,7 +667,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Employment relationships stay with People; payroll accounting and remittances normally stay with Finance.</t>
+          <t>Keep employment arrangements in People. Keep payroll accounting and remittances in Finance.</t>
         </is>
       </c>
     </row>
@@ -606,7 +677,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Physical asset records stay with Assets; stock movement and control stay with Inventory.</t>
+          <t>Keep equipment and property records in Assets. Keep stock quantities and movement in Inventory.</t>
         </is>
       </c>
     </row>
@@ -616,7 +687,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Claims and incidents stay with Risk; formal licence and compliance evidence stay with Compliance.</t>
+          <t>Keep claims and incidents in Risk. Keep licences and required compliance records in Compliance.</t>
         </is>
       </c>
     </row>
@@ -626,7 +697,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>System ownership, access, configuration, recovery, and technology services stay with Technology.</t>
+          <t>Keep system setup, access and recovery information in Technology. Do not include passwords or recovery codes.</t>
         </is>
       </c>
     </row>
@@ -636,7 +707,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Recurring methods stay with Operations; future direction with Strategy; reusable handoff knowledge with Knowledge.</t>
+          <t>Keep repeatable instructions in Operations, future plans in Strategy, and reusable lessons or handover notes in Knowledge.</t>
         </is>
       </c>
     </row>
@@ -646,11 +717,14 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Never displace a required legal, regulatory, accounting, payroll, or contractual system of record.</t>
+          <t>Keep required originals, backups and records in the systems your legal, accounting or other obligations require. This guide does not replace them.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -672,461 +746,461 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Taxonomy</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Fifteen stable record families. Use the responsibility and “Use when” columns to classify ambiguous records.</t>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Fifteen categories. The examples and Use when column help you choose a suitable home.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>What belongs here</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Business responsibility</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>What it supports</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Examples</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Use when</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Governance &amp; ownership</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Records that establish the business entity, ownership, formal authority, governance structure, or major company decisions.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Ownership and formal company authority.</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>• articles or certificate of incorporation
 • shareholder or ownership register</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Entity, ownership, formal authority, or governance action is the primary responsibility.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Finance, accounting &amp; tax</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Accounting books, transaction evidence, banking, receivables and payables, expenses, reconciliations, financial reporting, tax, and financial-remittance records.</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Bookkeeping, cash, financial reporting, tax, and transaction evidence.</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>• sales invoice
 • purchase invoice</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>The record primarily evidences, records, reconciles, reports, pays, collects, or supports a financial/tax obligation.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Customers &amp; revenue</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Records that define, develop, manage, or document customer relationships, commercial opportunities, sales commitments, and ongoing customer accounts.</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Sales and the ongoing customer relationship.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>• lead or opportunity record
 • proposal</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>The commercial customer relationship is primary; specific execution belongs with Projects.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Vendors &amp; procurement</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Records used to source, evaluate, select, order from, manage, and communicate with suppliers and service providers.</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Purchasing and supplier management.</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>• supplier profile
 • supplier quote</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Choosing, ordering from, or managing a supplier is primary; transaction evidence normally belongs with Finance.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>People &amp; workforce</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Employment, contractor, role, compensation-administration, time, training, performance, and other workforce records about people working for or with the business.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Employment and contractor administration.</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>• employment agreement
 • contractor agreement</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>The working relationship or workforce administration is primary; payroll accounting/remittance evidence normally belongs with Finance.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Projects, jobs &amp; delivery</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Records that define, execute, change, approve, evidence, complete, or hand off specific customer work, projects, jobs, engagements, or deliverables.</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Delivery of the specific job, project, or engagement.</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>• work order
 • statement of work</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Execution or delivery of a defined job, project, engagement, or deliverable is primary.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Operations &amp; procedures</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Recurring operating procedures, checklists, schedules, instructions, quality methods, and routine process records used to run the business consistently.</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>The recurring process or operating method.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>• standard operating procedure
 • recurring checklist</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>A repeatable operating method is primary; topic-specific notes/checklists stay with their actual subject.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Assets &amp; facilities</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Records that identify, assign, operate, service, inspect, repair, warrant, or manage physical assets, equipment, vehicles, tools, premises, and facilities.</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>The asset, equipment, vehicle, premises, or facility.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>• asset register
 • vehicle or equipment record</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Asset identity, custody, condition, operation, maintenance, warranty, inspection, or facilities management is primary.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Inventory &amp; supplies</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Records used to identify, count, receive, store, issue, consume, reorder, adjust, or trace inventory, stock, materials, and recurring supplies.</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Stock availability, movement, and material control.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>• SKU or item master
 • stock count</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Stock or supply control is primary; supplier selection stays with Vendors and invoices stay with Finance.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Insurance, risk &amp; incidents</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Insurance policies and certificates, claims, risk assessments, incident records, damage evidence, loss events, and other records primarily used to understand or manage business risk.</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Insurance, claims, risk response, loss prevention, and incident handling.</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>• insurance policy
 • certificate of insurance</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Insurance, claims, risk, or incident handling is primary unless formal compliance evidence is the main purpose.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Compliance, licences &amp; safety</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Licences, permits, required certifications, regulated inspections, safety-program evidence, compliance records, and other material maintained primarily to demonstrate required permission or adherence.</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>The licence, safety duty, regulatory requirement, or compliance evidence.</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>• business licence
 • permit</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>A legal, regulatory, licensing, safety, or professional requirement is the record’s main purpose.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Technology, access &amp; data</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Records that define, operate, administer, secure, recover, or document business systems, software, accounts, access, data handling, and technology services.</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>The system, account, access model, configuration, data process, backup, or technology service.</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>• system inventory
 • software subscription record</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>The system, account, access model, configuration, data process, backup, or technology service is primary.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Marketing &amp; brand</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Brand standards, creative assets, campaigns, content, advertising, media, messaging, publication, and other records used to present and promote the business.</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>The brand, campaign, content, public message, or marketing channel.</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>• brand guideline
 • logo or brand asset</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Brand or marketing work is primary; customer commercial records and financial invoices stay with their natural responsibilities.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Strategy &amp; planning</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Business plans, forecasts, priorities, market or internal research, roadmaps, strategic decisions, and records whose main purpose is choosing or directing future action.</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Future direction, priorities, and major initiatives.</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>• business plan
 • forecast used for planning</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>Forward-looking direction or planning is primary; books, delivery plans, and recurring procedures stay in operating categories.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Knowledge &amp; continuity</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Operational lessons, durable decision context, reference material, handoff notes, and other records whose main purpose is preserving what the business knows so work can continue across people and time.</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Reusable know-how, decision context, and continuity across people or time.</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>• lessons learned
 • handoff note</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Preserving reusable know-how or continuity is primary; do not use this as miscellaneous storage.</t>
         </is>
@@ -1134,6 +1208,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:E19"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1154,43 +1231,43 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Category Details</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Handling cues are practical review cues, not legal or regulatory classifications.</t>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Practical reminders about privacy and review, not legal classifications.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Handling cue</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Review trigger</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Common relationships</t>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Privacy reminder</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>When to review</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Related categories</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Governance &amp; ownership</t>
         </is>
@@ -1213,7 +1290,7 @@
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Finance, accounting &amp; tax</t>
         </is>
@@ -1236,7 +1313,7 @@
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Customers &amp; revenue</t>
         </is>
@@ -1259,7 +1336,7 @@
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Vendors &amp; procurement</t>
         </is>
@@ -1282,7 +1359,7 @@
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>People &amp; workforce</t>
         </is>
@@ -1305,7 +1382,7 @@
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Projects, jobs &amp; delivery</t>
         </is>
@@ -1328,7 +1405,7 @@
       </c>
     </row>
     <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Operations &amp; procedures</t>
         </is>
@@ -1351,7 +1428,7 @@
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Assets &amp; facilities</t>
         </is>
@@ -1374,7 +1451,7 @@
       </c>
     </row>
     <row r="13" ht="55" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Inventory &amp; supplies</t>
         </is>
@@ -1397,7 +1474,7 @@
       </c>
     </row>
     <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Insurance, risk &amp; incidents</t>
         </is>
@@ -1420,7 +1497,7 @@
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Compliance, licences &amp; safety</t>
         </is>
@@ -1443,7 +1520,7 @@
       </c>
     </row>
     <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Technology, access &amp; data</t>
         </is>
@@ -1466,7 +1543,7 @@
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Marketing &amp; brand</t>
         </is>
@@ -1489,7 +1566,7 @@
       </c>
     </row>
     <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; planning</t>
         </is>
@@ -1512,7 +1589,7 @@
       </c>
     </row>
     <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Knowledge &amp; continuity</t>
         </is>
@@ -1536,6 +1613,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:D19"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1554,45 +1634,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Implementation Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Optional fields for software, migrations, or structured record systems. The classification layer should point to authority rather than create a second source of truth.</t>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Optional technical fields for software and migrations. Keep a reference to the original or required system rather than replacing it.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Why it exists</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>primary_category_id</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Stable OSBRT category for primary operational meaning.</t>
+          <t>Stable OSBRT category for what the record is mainly used for.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>record_type</t>
         </is>
@@ -1604,19 +1684,19 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>responsible_business_area</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Responsibility that owns correctness; one person may fill several.</t>
+          <t>The business responsibility that keeps this record correct. One person may handle several.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1628,7 +1708,7 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>sensitivity</t>
         </is>
@@ -1640,7 +1720,7 @@
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>review_or_lifecycle_state</t>
         </is>
@@ -1652,7 +1732,7 @@
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>related_categories</t>
         </is>
@@ -1664,7 +1744,7 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>related_entities</t>
         </is>
@@ -1676,30 +1756,33 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>authority_reference</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pointer to the authoritative system/original; never store secrets here.</t>
+          <t>Reference to the original or required system. Do not put secrets here.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Authority rule</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Keep the original record</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Classify the record without displacing its authoritative system, signed original, regulated register, or other governing source. Never put passwords or recovery codes in authority references.</t>
+          <t>Use these fields to organize references. They do not replace signed originals, accounting records or required registers. Never put passwords or recovery codes in a reference.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
+++ b/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Taxonomy'!$A$4:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Category Details'!$A$4:$D$19</definedName>
   </definedNames>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,42 +65,8 @@
     <font>
       <color rgb="001F2933"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF1F2933"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <color rgb="FF5B6573"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF1E6B52"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF1F2933"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF1F2933"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF1F2933"/>
-    </font>
-    <font>
-      <color rgb="FF1F2933"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -115,16 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F7F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF172033"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,33 +132,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -577,45 +506,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Small Business Records Filing Guide</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Choose where a record belongs by the work it supports. One person may handle several kinds of work. Guide version 0.1.1, 17 September 2026.</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Choose where a record belongs by the work it supports. These categories work for a one-person business as well as a larger team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Start with the purpose</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>What do you need this record for, and where would you look for it?</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Where would you look?</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>If this record went missing or became out of date, which part of the business would need it fixed?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>For a small business</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>For small businesses</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>You do not need a department for each category. Use only the categories that help you find and maintain records.</t>
-        </is>
-      </c>
-    </row>
+          <t>The categories describe responsibilities, not departments. You do not need a separate person for each one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>When two categories both seem right</t>
         </is>
@@ -627,7 +558,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Choose by purpose, not whether the record is an email, PDF or spreadsheet.</t>
+          <t>Choose by what the record is mainly used for, not its file format or the name of a department.</t>
         </is>
       </c>
     </row>
@@ -637,7 +568,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Keep invoices, payments and accounting records in Finance.</t>
+          <t>Keep invoices, payments and other financial transaction records in Finance when that is their main purpose.</t>
         </is>
       </c>
     </row>
@@ -647,7 +578,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Keep customer details in Customers. Keep the work on a particular job in Projects.</t>
+          <t>Keep the ongoing customer relationship in Customers and work for a specific job in Projects.</t>
         </is>
       </c>
     </row>
@@ -657,7 +588,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Keep supplier selection and ordering in Vendors. Keep purchase invoices in Finance.</t>
+          <t>Keep buying decisions and supplier arrangements in Vendors. The resulting invoice normally belongs in Finance.</t>
         </is>
       </c>
     </row>
@@ -667,7 +598,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Keep employment arrangements in People. Keep payroll accounting and remittances in Finance.</t>
+          <t>Keep employment arrangements in People. Payroll accounts and remittance records normally belong in Finance.</t>
         </is>
       </c>
     </row>
@@ -677,7 +608,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Keep equipment and property records in Assets. Keep stock quantities and movement in Inventory.</t>
+          <t>Keep equipment and other physical asset records in Assets. Keep stock movements and stock control in Inventory.</t>
         </is>
       </c>
     </row>
@@ -687,7 +618,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Keep claims and incidents in Risk. Keep licences and required compliance records in Compliance.</t>
+          <t>Keep claims and incidents in Risk. Keep licences and proof of required compliance in Compliance.</t>
         </is>
       </c>
     </row>
@@ -697,7 +628,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Keep system setup, access and recovery information in Technology. Do not include passwords or recovery codes.</t>
+          <t>Keep software, devices, account access, settings and recovery arrangements in Technology.</t>
         </is>
       </c>
     </row>
@@ -707,7 +638,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Keep repeatable instructions in Operations, future plans in Strategy, and reusable lessons or handover notes in Knowledge.</t>
+          <t>Keep repeated ways of working in Operations, future plans in Strategy, and reusable handover information in Knowledge.</t>
         </is>
       </c>
     </row>
@@ -717,14 +648,11 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Keep required originals, backups and records in the systems your legal, accounting or other obligations require. This guide does not replace them.</t>
+          <t>Keep any legally or contractually required record in its required system. This filing guide does not replace accounting, payroll or official records.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -746,461 +674,462 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Taxonomy</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Fifteen categories. The examples and Use when column help you choose a suitable home.</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fifteen stable record families. Use the responsibility and “Use when” columns to classify ambiguous records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>What belongs here</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>What it supports</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Business responsibility</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Examples</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Use when</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Governance &amp; ownership</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Records that establish the business entity, ownership, formal authority, governance structure, or major company decisions.</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Ownership and formal company authority.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>• articles or certificate of incorporation
 • shareholder or ownership register</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Entity, ownership, formal authority, or governance action is the primary responsibility.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Finance, accounting &amp; tax</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Accounting books, transaction evidence, banking, receivables and payables, expenses, reconciliations, financial reporting, tax, and financial-remittance records.</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Bookkeeping, cash, financial reporting, tax, and transaction evidence.</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>• sales invoice
 • purchase invoice</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>The record primarily evidences, records, reconciles, reports, pays, collects, or supports a financial/tax obligation.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Customers &amp; revenue</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Records that define, develop, manage, or document customer relationships, commercial opportunities, sales commitments, and ongoing customer accounts.</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Sales and the ongoing customer relationship.</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>• lead or opportunity record
 • proposal</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>The commercial customer relationship is primary; specific execution belongs with Projects.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Vendors &amp; procurement</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Records used to source, evaluate, select, order from, manage, and communicate with suppliers and service providers.</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Purchasing and supplier management.</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>• supplier profile
 • supplier quote</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Choosing, ordering from, or managing a supplier is primary; transaction evidence normally belongs with Finance.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>People &amp; workforce</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Employment, contractor, role, compensation-administration, time, training, performance, and other workforce records about people working for or with the business.</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Employment and contractor administration.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>• employment agreement
 • contractor agreement</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>The working relationship or workforce administration is primary; payroll accounting/remittance evidence normally belongs with Finance.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Projects, jobs &amp; delivery</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Records that define, execute, change, approve, evidence, complete, or hand off specific customer work, projects, jobs, engagements, or deliverables.</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Delivery of the specific job, project, or engagement.</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>• work order
 • statement of work</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Execution or delivery of a defined job, project, engagement, or deliverable is primary.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Operations &amp; procedures</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Recurring operating procedures, checklists, schedules, instructions, quality methods, and routine process records used to run the business consistently.</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>The recurring process or operating method.</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>• standard operating procedure
 • recurring checklist</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>A repeatable operating method is primary; topic-specific notes/checklists stay with their actual subject.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Assets &amp; facilities</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Records that identify, assign, operate, service, inspect, repair, warrant, or manage physical assets, equipment, vehicles, tools, premises, and facilities.</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>The asset, equipment, vehicle, premises, or facility.</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>• asset register
 • vehicle or equipment record</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Asset identity, custody, condition, operation, maintenance, warranty, inspection, or facilities management is primary.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Inventory &amp; supplies</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Records used to identify, count, receive, store, issue, consume, reorder, adjust, or trace inventory, stock, materials, and recurring supplies.</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Stock availability, movement, and material control.</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>• SKU or item master
 • stock count</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Stock or supply control is primary; supplier selection stays with Vendors and invoices stay with Finance.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Insurance, risk &amp; incidents</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Insurance policies and certificates, claims, risk assessments, incident records, damage evidence, loss events, and other records primarily used to understand or manage business risk.</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Insurance, claims, risk response, loss prevention, and incident handling.</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>• insurance policy
 • certificate of insurance</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Insurance, claims, risk, or incident handling is primary unless formal compliance evidence is the main purpose.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Compliance, licences &amp; safety</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Licences, permits, required certifications, regulated inspections, safety-program evidence, compliance records, and other material maintained primarily to demonstrate required permission or adherence.</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>The licence, safety duty, regulatory requirement, or compliance evidence.</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>• business licence
 • permit</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>A legal, regulatory, licensing, safety, or professional requirement is the record’s main purpose.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Technology, access &amp; data</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Records that define, operate, administer, secure, recover, or document business systems, software, accounts, access, data handling, and technology services.</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>The system, account, access model, configuration, data process, backup, or technology service.</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>• system inventory
 • software subscription record</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>The system, account, access model, configuration, data process, backup, or technology service is primary.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Marketing &amp; brand</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Brand standards, creative assets, campaigns, content, advertising, media, messaging, publication, and other records used to present and promote the business.</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>The brand, campaign, content, public message, or marketing channel.</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>• brand guideline
 • logo or brand asset</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Brand or marketing work is primary; customer commercial records and financial invoices stay with their natural responsibilities.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Strategy &amp; planning</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Business plans, forecasts, priorities, market or internal research, roadmaps, strategic decisions, and records whose main purpose is choosing or directing future action.</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Future direction, priorities, and major initiatives.</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>• business plan
 • forecast used for planning</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Forward-looking direction or planning is primary; books, delivery plans, and recurring procedures stay in operating categories.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Knowledge &amp; continuity</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Operational lessons, durable decision context, reference material, handoff notes, and other records whose main purpose is preserving what the business knows so work can continue across people and time.</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Reusable know-how, decision context, and continuity across people or time.</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>• lessons learned
 • handoff note</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Preserving reusable know-how or continuity is primary; do not use this as miscellaneous storage.</t>
         </is>
@@ -1208,9 +1137,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:E19"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1231,43 +1157,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category Details</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Practical reminders about privacy and review, not legal classifications.</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Handling cues are practical review cues, not legal or regulatory classifications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Privacy reminder</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>When to review</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Related categories</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Handling cue</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Review trigger</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Common relationships</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Governance &amp; ownership</t>
         </is>
@@ -1290,7 +1217,7 @@
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Finance, accounting &amp; tax</t>
         </is>
@@ -1313,7 +1240,7 @@
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Customers &amp; revenue</t>
         </is>
@@ -1336,7 +1263,7 @@
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Vendors &amp; procurement</t>
         </is>
@@ -1359,7 +1286,7 @@
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>People &amp; workforce</t>
         </is>
@@ -1382,7 +1309,7 @@
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Projects, jobs &amp; delivery</t>
         </is>
@@ -1405,7 +1332,7 @@
       </c>
     </row>
     <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Operations &amp; procedures</t>
         </is>
@@ -1428,7 +1355,7 @@
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Assets &amp; facilities</t>
         </is>
@@ -1451,7 +1378,7 @@
       </c>
     </row>
     <row r="13" ht="55" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Inventory &amp; supplies</t>
         </is>
@@ -1474,7 +1401,7 @@
       </c>
     </row>
     <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Insurance, risk &amp; incidents</t>
         </is>
@@ -1497,7 +1424,7 @@
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Compliance, licences &amp; safety</t>
         </is>
@@ -1520,7 +1447,7 @@
       </c>
     </row>
     <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Technology, access &amp; data</t>
         </is>
@@ -1543,7 +1470,7 @@
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Marketing &amp; brand</t>
         </is>
@@ -1566,7 +1493,7 @@
       </c>
     </row>
     <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Strategy &amp; planning</t>
         </is>
@@ -1589,7 +1516,7 @@
       </c>
     </row>
     <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Knowledge &amp; continuity</t>
         </is>
@@ -1613,9 +1540,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:D19"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1634,33 +1558,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Implementation Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Optional technical fields for software and migrations. Keep a reference to the original or required system rather than replacing it.</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Optional fields for software and structured records. Link to the original record or current system rather than maintaining another competing copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Why it exists</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>primary_category_id</t>
         </is>
@@ -1672,7 +1597,7 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>record_type</t>
         </is>
@@ -1684,19 +1609,19 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>responsible_business_area</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>The business responsibility that keeps this record correct. One person may handle several.</t>
+          <t>Responsibility that owns correctness; one person may fill several.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1708,7 +1633,7 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>sensitivity</t>
         </is>
@@ -1720,7 +1645,7 @@
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>review_or_lifecycle_state</t>
         </is>
@@ -1732,7 +1657,7 @@
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>related_categories</t>
         </is>
@@ -1744,7 +1669,7 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>related_entities</t>
         </is>
@@ -1756,33 +1681,32 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>authority_reference</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Reference to the original or required system. Do not put secrets here.</t>
-        </is>
-      </c>
-    </row>
+          <t>Pointer to the authoritative system/original; never store secrets here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Keep the original record</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Authority rule</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Use these fields to organize references. They do not replace signed originals, accounting records or required registers. Never put passwords or recovery codes in a reference.</t>
+          <t>Use categories to help find records. Keep the signed original and any required official, accounting or payroll record in its proper place. Do not enter passwords or recovery codes here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
+++ b/taxonomies/open-small-business-records-taxonomy/taxonomy.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Taxonomy'!$A$4:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Category Details'!$A$4:$D$19</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -508,41 +508,43 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Small Business Records Taxonomy</t>
+          <t>Small Business Records Filing Guide</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Start here. The taxonomy describes business responsibilities, not departments or headcount.</t>
-        </is>
-      </c>
-    </row>
+          <t>Choose where a record belongs by the work it supports. These categories work for a one-person business as well as a larger team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Primary question</t>
+          <t>Where would you look?</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>If this record became wrong or disappeared tomorrow, which business responsibility would have to fix the problem?</t>
+          <t>If this record went missing or became out of date, which part of the business would need it fixed?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Small-business rule</t>
+          <t>For small businesses</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Categories describe responsibilities, not departments. One person can own several responsibilities.</t>
-        </is>
-      </c>
-    </row>
+          <t>The categories describe responsibilities, not departments. You do not need a separate person for each one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
@@ -556,7 +558,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Responsibility beats file format, document type, and department name.</t>
+          <t>Choose by what the record is mainly used for, not its file format or the name of a department.</t>
         </is>
       </c>
     </row>
@@ -566,7 +568,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Financial transaction evidence stays in Finance when finance is its primary purpose.</t>
+          <t>Keep invoices, payments and other financial transaction records in Finance when that is their main purpose.</t>
         </is>
       </c>
     </row>
@@ -576,7 +578,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Customer relationships stay with Customers; specific execution stays with Projects.</t>
+          <t>Keep the ongoing customer relationship in Customers and work for a specific job in Projects.</t>
         </is>
       </c>
     </row>
@@ -586,7 +588,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Procurement stays with Vendors; resulting purchase invoices normally stay with Finance.</t>
+          <t>Keep buying decisions and supplier arrangements in Vendors. The resulting invoice normally belongs in Finance.</t>
         </is>
       </c>
     </row>
@@ -596,7 +598,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Employment relationships stay with People; payroll accounting and remittances normally stay with Finance.</t>
+          <t>Keep employment arrangements in People. Payroll accounts and remittance records normally belong in Finance.</t>
         </is>
       </c>
     </row>
@@ -606,7 +608,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Physical asset records stay with Assets; stock movement and control stay with Inventory.</t>
+          <t>Keep equipment and other physical asset records in Assets. Keep stock movements and stock control in Inventory.</t>
         </is>
       </c>
     </row>
@@ -616,7 +618,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Claims and incidents stay with Risk; formal licence and compliance evidence stay with Compliance.</t>
+          <t>Keep claims and incidents in Risk. Keep licences and proof of required compliance in Compliance.</t>
         </is>
       </c>
     </row>
@@ -626,7 +628,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>System ownership, access, configuration, recovery, and technology services stay with Technology.</t>
+          <t>Keep software, devices, account access, settings and recovery arrangements in Technology.</t>
         </is>
       </c>
     </row>
@@ -636,7 +638,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Recurring methods stay with Operations; future direction with Strategy; reusable handoff knowledge with Knowledge.</t>
+          <t>Keep repeated ways of working in Operations, future plans in Strategy, and reusable handover information in Knowledge.</t>
         </is>
       </c>
     </row>
@@ -646,7 +648,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Never displace a required legal, regulatory, accounting, payroll, or contractual system of record.</t>
+          <t>Keep any legally or contractually required record in its required system. This filing guide does not replace accounting, payroll or official records.</t>
         </is>
       </c>
     </row>
@@ -685,6 +687,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1167,6 +1170,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1563,10 +1567,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Optional fields for software, migrations, or structured record systems. The classification layer should point to authority rather than create a second source of truth.</t>
-        </is>
-      </c>
-    </row>
+          <t>Optional fields for software and structured records. Link to the original record or current system rather than maintaining another competing copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1587,7 +1592,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Stable OSBRT category for primary operational meaning.</t>
+          <t>Stable OSBRT category for what the record is mainly used for.</t>
         </is>
       </c>
     </row>
@@ -1687,6 +1692,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1695,7 +1702,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Classify the record without displacing its authoritative system, signed original, regulated register, or other governing source. Never put passwords or recovery codes in authority references.</t>
+          <t>Use categories to help find records. Keep the signed original and any required official, accounting or payroll record in its proper place. Do not enter passwords or recovery codes here.</t>
         </is>
       </c>
     </row>
